--- a/i18n-demo/docs/i18n三方案对比.xlsx
+++ b/i18n-demo/docs/i18n三方案对比.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>translations.json（经 loadTranslations 注册）</t>
+          <t>assets/locale/{zh,en,de}.json（按 locale 加载，loadTranslations 注）</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>translations.json（唯一总表）+ 生成 registry</t>
+          <t>translations.json（唯一主文件，脚本源）+ assets/locale/*.json（运行时加载）</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>一种文本数据格式，用 { 键: 值 } 描述数据；本项目的文案总表就是 JSON。</t>
+          <t>运行时方案与自研方案的主文件（translations.json），运行时按 locale 加载其拆分出的 assets/locale/*.json</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>三方案共用的文案总表（键 → {语言: 文本}）</t>
+          <t>运行时方案与自研方案的主文件（translations.json），运行时按 locale 加载其拆分出的 assets/locale/*.json</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>运行时方案与自研方案的文案总表</t>
+          <t>运行时方案与自研方案的主文件（translations.json），运行时按 locale 加载其拆分出的 assets/locale/*.json</t>
         </is>
       </c>
     </row>

--- a/i18n-demo/docs/i18n三方案对比.xlsx
+++ b/i18n-demo/docs/i18n三方案对比.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>assets/locale/{zh,en,de}.json（按 locale 加载，loadTranslations 注）</t>
+          <t>translations.json（经 loadTranslations 注册）</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>translations.json（唯一主文件，脚本源）+ assets/locale/*.json（运行时加载）</t>
+          <t>translations.json（唯一总表）+ 生成 registry</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>运行时方案与自研方案的主文件（translations.json），运行时按 locale 加载其拆分出的 assets/locale/*.json</t>
+          <t>一种文本数据格式，用 { 键: 值 } 描述数据；本项目的文案总表就是 JSON。</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>运行时方案与自研方案的主文件（translations.json），运行时按 locale 加载其拆分出的 assets/locale/*.json</t>
+          <t>三方案共用的文案总表（键 → {语言: 文本}）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>运行时方案与自研方案的主文件（translations.json），运行时按 locale 加载其拆分出的 assets/locale/*.json</t>
+          <t>运行时方案与自研方案的文案总表</t>
         </is>
       </c>
     </row>
